--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MISSISSIPPI_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MISSISSIPPI_2014.xlsx
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C76">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C148">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C154">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C321">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C581">
